--- a/data/dividends_info_20260605.xlsx
+++ b/data/dividends_info_20260605.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>64.04000091552734</v>
+        <v>62.81999969482422</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1405371622631853</v>
+        <v>0.1432664763406791</v>
       </c>
       <c r="J2" t="n">
         <v>283</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>56</v>
+        <v>55.65000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.25</v>
+        <v>1.257861600730557</v>
       </c>
       <c r="J3" t="n">
         <v>262</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4819999933242798</v>
+        <v>0.4639999866485596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8298755301660101</v>
+        <v>0.8620689903229801</v>
       </c>
       <c r="J5" t="n">
         <v>192</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>64.04000091552734</v>
+        <v>62.81999969482422</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1405371622631853</v>
+        <v>0.1432664763406791</v>
       </c>
       <c r="J6" t="n">
         <v>192</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.089999914169312</v>
+        <v>2.065000057220459</v>
       </c>
       <c r="I7" t="n">
-        <v>3.68421067761643</v>
+        <v>3.728813455997861</v>
       </c>
       <c r="J7" t="n">
         <v>171</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.43499946594238</v>
+        <v>23.54999923706055</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1521229193642</v>
+        <v>1.146496852429201</v>
       </c>
       <c r="J8" t="n">
         <v>171</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.53000020980835</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="I9" t="n">
-        <v>3.616636390813651</v>
+        <v>3.66300363741163</v>
       </c>
       <c r="J9" t="n">
         <v>164</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.4819999933242798</v>
+        <v>0.4639999866485596</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8298755301660101</v>
+        <v>0.8620689903229801</v>
       </c>
       <c r="J11" t="n">
         <v>136</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.44000053405762</v>
+        <v>23.54999923706055</v>
       </c>
       <c r="I14" t="n">
-        <v>1.151877106861402</v>
+        <v>1.146496852429201</v>
       </c>
       <c r="J14" t="n">
         <v>108</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>64.04000091552734</v>
+        <v>62.81999969482422</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1405371622631853</v>
+        <v>0.1432664763406791</v>
       </c>
       <c r="J15" t="n">
         <v>108</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.980000019073486</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="I16" t="n">
-        <v>5.016722392025687</v>
+        <v>5.050505001853162</v>
       </c>
       <c r="J16" t="n">
         <v>101</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.4819999933242798</v>
+        <v>0.4639999866485596</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8298755301660101</v>
+        <v>0.8620689903229801</v>
       </c>
       <c r="J17" t="n">
         <v>80</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>5.96999979019165</v>
       </c>
       <c r="I19" t="n">
-        <v>4.166666666666666</v>
+        <v>4.187604837285504</v>
       </c>
       <c r="J19" t="n">
         <v>52</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.360000133514404</v>
+        <v>4.269999980926514</v>
       </c>
       <c r="I20" t="n">
-        <v>3.211009075982577</v>
+        <v>3.278688539235603</v>
       </c>
       <c r="J20" t="n">
         <v>45</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.64799976348877</v>
+        <v>9.637999534606934</v>
       </c>
       <c r="I21" t="n">
-        <v>2.694859104204441</v>
+        <v>2.69765524543163</v>
       </c>
       <c r="J21" t="n">
         <v>45</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>15.07999992370605</v>
+        <v>14.84000015258789</v>
       </c>
       <c r="I22" t="n">
-        <v>3.978779860978569</v>
+        <v>4.04312664306387</v>
       </c>
       <c r="J22" t="n">
         <v>45</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.677999973297119</v>
+        <v>3.608000040054321</v>
       </c>
       <c r="I23" t="n">
-        <v>5.98151173456324</v>
+        <v>6.097560907917499</v>
       </c>
       <c r="J23" t="n">
         <v>45</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.4819999933242798</v>
+        <v>0.4639999866485596</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8298755301660101</v>
+        <v>0.8620689903229801</v>
       </c>
       <c r="J24" t="n">
         <v>45</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.050000190734863</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>1.652892509873682</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="J25" t="n">
         <v>45</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18.54999923706055</v>
+        <v>18.64999961853027</v>
       </c>
       <c r="I26" t="n">
-        <v>2.026954261263794</v>
+        <v>2.016085832122022</v>
       </c>
       <c r="J26" t="n">
         <v>45</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.680000066757202</v>
+        <v>2.700000047683716</v>
       </c>
       <c r="I29" t="n">
-        <v>5.597014785954832</v>
+        <v>5.555555457440915</v>
       </c>
       <c r="J29" t="n">
         <v>38</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.119999885559082</v>
+        <v>2.140000104904175</v>
       </c>
       <c r="I30" t="n">
-        <v>4.009434178699683</v>
+        <v>3.971962422114281</v>
       </c>
       <c r="J30" t="n">
         <v>31</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.400000095367432</v>
+        <v>4.389999866485596</v>
       </c>
       <c r="I31" t="n">
-        <v>1.590909056427066</v>
+        <v>1.594533078107776</v>
       </c>
       <c r="J31" t="n">
         <v>31</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>34.79999923706055</v>
+        <v>33.59999847412109</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4310344922084259</v>
+        <v>0.446428591702261</v>
       </c>
       <c r="J32" t="n">
         <v>31</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.650000095367432</v>
+        <v>5.849999904632568</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7079645898200416</v>
+        <v>0.6837606949074361</v>
       </c>
       <c r="J33" t="n">
         <v>24</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>23</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="I34" t="n">
-        <v>4.130434782608695</v>
+        <v>4.148471684826042</v>
       </c>
       <c r="J34" t="n">
         <v>17</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>30.10000038146973</v>
+        <v>30.45000076293945</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6478405233511114</v>
+        <v>0.640394072624568</v>
       </c>
       <c r="J35" t="n">
         <v>17</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.835000038146973</v>
+        <v>1.820000052452087</v>
       </c>
       <c r="I36" t="n">
-        <v>1.798365085230418</v>
+        <v>1.813186760931082</v>
       </c>
       <c r="J36" t="n">
         <v>17</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.244999885559082</v>
+        <v>5.21999979019165</v>
       </c>
       <c r="I37" t="n">
-        <v>5.529075430458049</v>
+        <v>5.555555778850955</v>
       </c>
       <c r="J37" t="n">
         <v>17</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.812000036239624</v>
+        <v>3.828000068664551</v>
       </c>
       <c r="I38" t="n">
-        <v>4.19727173344503</v>
+        <v>4.179728242685695</v>
       </c>
       <c r="J38" t="n">
         <v>17</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.660000085830688</v>
+        <v>2.657999992370605</v>
       </c>
       <c r="I39" t="n">
-        <v>5.210526147660508</v>
+        <v>5.214446967563233</v>
       </c>
       <c r="J39" t="n">
         <v>17</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>51.65000152587891</v>
+        <v>51.86000061035156</v>
       </c>
       <c r="I40" t="n">
-        <v>1.21974826987051</v>
+        <v>1.214809087129568</v>
       </c>
       <c r="J40" t="n">
         <v>17</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>6.025000095367432</v>
       </c>
       <c r="I41" t="n">
-        <v>2.333333333333333</v>
+        <v>2.323651415501964</v>
       </c>
       <c r="J41" t="n">
         <v>17</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>19.14999961853027</v>
+        <v>18.75</v>
       </c>
       <c r="I42" t="n">
-        <v>4.073107130745016</v>
+        <v>4.16</v>
       </c>
       <c r="J42" t="n">
         <v>17</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>25.80999946594238</v>
+        <v>25.75</v>
       </c>
       <c r="I43" t="n">
-        <v>3.293297239783435</v>
+        <v>3.300970873786407</v>
       </c>
       <c r="J43" t="n">
         <v>17</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>64.04000091552734</v>
+        <v>62.81999969482422</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1405371622631853</v>
+        <v>0.1432664763406791</v>
       </c>
       <c r="J44" t="n">
         <v>17</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.389999985694885</v>
+        <v>1.370000004768372</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7194244678355752</v>
+        <v>0.7299270047587131</v>
       </c>
       <c r="J45" t="n">
         <v>17</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.282000064849854</v>
+        <v>6.296000003814697</v>
       </c>
       <c r="I46" t="n">
-        <v>2.886023529583221</v>
+        <v>2.879606097365815</v>
       </c>
       <c r="J46" t="n">
         <v>17</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8.729999542236328</v>
+        <v>8.640000343322754</v>
       </c>
       <c r="I47" t="n">
-        <v>2.978236124092589</v>
+        <v>3.009259139682045</v>
       </c>
       <c r="J47" t="n">
         <v>17</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.02499961853027</v>
+        <v>10.05000019073486</v>
       </c>
       <c r="I48" t="n">
-        <v>2.763092374467441</v>
+        <v>2.75621885316348</v>
       </c>
       <c r="J48" t="n">
         <v>17</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.089999914169312</v>
+        <v>3.046000003814697</v>
       </c>
       <c r="I50" t="n">
-        <v>3.559870649044061</v>
+        <v>3.611293495149051</v>
       </c>
       <c r="J50" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2.099999904632568</v>
+        <v>1.980000019073486</v>
       </c>
       <c r="I51" t="n">
-        <v>1.142857194757788</v>
+        <v>1.212121200444759</v>
       </c>
       <c r="J51" t="n">
         <v>10</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.204999923706055</v>
+        <v>3.190000057220459</v>
       </c>
       <c r="I52" t="n">
-        <v>4.992199806825155</v>
+        <v>5.015673891222834</v>
       </c>
       <c r="J52" t="n">
         <v>3</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8899999856948853</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="I53" t="n">
-        <v>2.808988809194278</v>
+        <v>2.777777851363761</v>
       </c>
       <c r="J53" t="n">
         <v>3</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>26.85000038146973</v>
+        <v>26.75</v>
       </c>
       <c r="I54" t="n">
-        <v>4.134078153555842</v>
+        <v>4.149532710280375</v>
       </c>
       <c r="J54" t="n">
         <v>-1</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.9039999842643738</v>
+        <v>0.8960000276565552</v>
       </c>
       <c r="I55" t="n">
-        <v>3.318584128561946</v>
+        <v>3.348214182365993</v>
       </c>
       <c r="J55" t="n">
         <v>-4</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4799999892711639</v>
+        <v>0.4819999933242798</v>
       </c>
       <c r="I56" t="n">
-        <v>4.791666773768765</v>
+        <v>4.771784298454558</v>
       </c>
       <c r="J56" t="n">
         <v>-4</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>19.20000076293945</v>
+        <v>19.5</v>
       </c>
       <c r="I57" t="n">
-        <v>3.124999875823662</v>
+        <v>3.076923076923077</v>
       </c>
       <c r="J57" t="n">
         <v>-4</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.319999694824219</v>
+        <v>9.380000114440918</v>
       </c>
       <c r="I58" t="n">
-        <v>2.145922817047604</v>
+        <v>2.132196136032998</v>
       </c>
       <c r="J58" t="n">
         <v>-4</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.359999895095825</v>
+        <v>2.315000057220459</v>
       </c>
       <c r="I59" t="n">
-        <v>7.627118983100263</v>
+        <v>7.775377777576378</v>
       </c>
       <c r="J59" t="n">
         <v>-11</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.399999618530273</v>
+        <v>8.350000381469727</v>
       </c>
       <c r="I60" t="n">
-        <v>3.571428733618088</v>
+        <v>3.592814207119778</v>
       </c>
       <c r="J60" t="n">
         <v>-11</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>15.96000003814697</v>
+        <v>15.57999992370605</v>
       </c>
       <c r="I61" t="n">
-        <v>1.566416036356264</v>
+        <v>1.604621317228684</v>
       </c>
       <c r="J61" t="n">
         <v>-11</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3.890000104904175</v>
+        <v>3.839999914169312</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7712082054234035</v>
+        <v>0.7812500174622986</v>
       </c>
       <c r="J62" t="n">
         <v>-11</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>4.25</v>
+        <v>4.159999847412109</v>
       </c>
       <c r="I63" t="n">
-        <v>3.529411764705882</v>
+        <v>3.605769363028063</v>
       </c>
       <c r="J63" t="n">
         <v>-11</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12.69999980926514</v>
+        <v>12.60000038146973</v>
       </c>
       <c r="I64" t="n">
-        <v>4.566929202446662</v>
+        <v>4.603174463811769</v>
       </c>
       <c r="J64" t="n">
         <v>-11</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2.260999917984009</v>
+        <v>2.242000102996826</v>
       </c>
       <c r="I65" t="n">
-        <v>4.599734797546134</v>
+        <v>4.638715219548196</v>
       </c>
       <c r="J65" t="n">
         <v>-18</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>10.95499992370605</v>
+        <v>10.71500015258789</v>
       </c>
       <c r="I66" t="n">
-        <v>2.647193080964382</v>
+        <v>2.706486195709097</v>
       </c>
       <c r="J66" t="n">
         <v>-18</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2.089999914169312</v>
+        <v>2.065000057220459</v>
       </c>
       <c r="I67" t="n">
-        <v>3.68421067761643</v>
+        <v>3.728813455997861</v>
       </c>
       <c r="J67" t="n">
         <v>-18</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>38.5099983215332</v>
+        <v>38.81000137329102</v>
       </c>
       <c r="I68" t="n">
-        <v>4.25863430662104</v>
+        <v>4.225714872374741</v>
       </c>
       <c r="J68" t="n">
         <v>-18</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>35</v>
+        <v>34.84000015258789</v>
       </c>
       <c r="I69" t="n">
-        <v>5.714285714285714</v>
+        <v>5.740528103446181</v>
       </c>
       <c r="J69" t="n">
         <v>-18</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3.296000003814697</v>
+        <v>3.24399995803833</v>
       </c>
       <c r="I70" t="n">
-        <v>3.033980579012828</v>
+        <v>3.082614096594216</v>
       </c>
       <c r="J70" t="n">
         <v>-18</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>38.68000030517578</v>
+        <v>38.34000015258789</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3838159225147021</v>
+        <v>0.3872196124390969</v>
       </c>
       <c r="J71" t="n">
         <v>-18</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>20.23999977111816</v>
+        <v>19.98999977111816</v>
       </c>
       <c r="I72" t="n">
-        <v>4.545454596856324</v>
+        <v>4.602301203270793</v>
       </c>
       <c r="J72" t="n">
         <v>-18</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>11.27000045776367</v>
+        <v>11.22999954223633</v>
       </c>
       <c r="I73" t="n">
-        <v>2.661934230830808</v>
+        <v>2.671415959294495</v>
       </c>
       <c r="J73" t="n">
         <v>-18</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>84.58000183105469</v>
+        <v>82.91999816894531</v>
       </c>
       <c r="I74" t="n">
-        <v>1.229605080970984</v>
+        <v>1.254220963537713</v>
       </c>
       <c r="J74" t="n">
         <v>-18</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>44.77000045776367</v>
+        <v>44.29999923706055</v>
       </c>
       <c r="I75" t="n">
-        <v>1.563547002105539</v>
+        <v>1.580135467393853</v>
       </c>
       <c r="J75" t="n">
         <v>-18</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>56</v>
+        <v>55.65000152587891</v>
       </c>
       <c r="I76" t="n">
-        <v>3.928571428571429</v>
+        <v>3.953279316581752</v>
       </c>
       <c r="J76" t="n">
         <v>-18</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>9.020000457763672</v>
+        <v>8.944999694824219</v>
       </c>
       <c r="I77" t="n">
-        <v>9.534367587085686</v>
+        <v>9.61430999821739</v>
       </c>
       <c r="J77" t="n">
         <v>-18</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>11.73600006103516</v>
+        <v>11.66600036621094</v>
       </c>
       <c r="I78" t="n">
-        <v>4.771642783636847</v>
+        <v>4.800274150701792</v>
       </c>
       <c r="J78" t="n">
         <v>-18</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>2.160000085830688</v>
+        <v>2.170000076293945</v>
       </c>
       <c r="I79" t="n">
-        <v>1.851851778265873</v>
+        <v>1.843317907541938</v>
       </c>
       <c r="J79" t="n">
         <v>-18</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>8.699999809265137</v>
+        <v>8.569999694824219</v>
       </c>
       <c r="I80" t="n">
-        <v>3.448275937667407</v>
+        <v>3.500583555226759</v>
       </c>
       <c r="J80" t="n">
         <v>-18</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>90</v>
+        <v>87.40000152587891</v>
       </c>
       <c r="I82" t="n">
-        <v>2.288888888888889</v>
+        <v>2.356979363884839</v>
       </c>
       <c r="J82" t="n">
         <v>-18</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>15.17000007629395</v>
+        <v>15.14000034332275</v>
       </c>
       <c r="I83" t="n">
-        <v>4.943968333737979</v>
+        <v>4.95376474896036</v>
       </c>
       <c r="J83" t="n">
         <v>-18</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>14.06999969482422</v>
+        <v>13.84000015258789</v>
       </c>
       <c r="I84" t="n">
-        <v>2.132196208293863</v>
+        <v>2.167630033905051</v>
       </c>
       <c r="J84" t="n">
         <v>-18</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>51</v>
+        <v>49.90000152587891</v>
       </c>
       <c r="I85" t="n">
-        <v>1.666666666666667</v>
+        <v>1.70340676153923</v>
       </c>
       <c r="J85" t="n">
         <v>-18</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>72.27999877929688</v>
+        <v>71.41999816894531</v>
       </c>
       <c r="I87" t="n">
-        <v>1.798561181454196</v>
+        <v>1.820218472877619</v>
       </c>
       <c r="J87" t="n">
         <v>-18</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>6.760000228881836</v>
+        <v>6.940000057220459</v>
       </c>
       <c r="I88" t="n">
-        <v>8.875739344453326</v>
+        <v>8.645533069927756</v>
       </c>
       <c r="J88" t="n">
         <v>-18</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>6.900000095367432</v>
+        <v>6.449999809265137</v>
       </c>
       <c r="I89" t="n">
-        <v>6.81159410875301</v>
+        <v>7.286821920907129</v>
       </c>
       <c r="J89" t="n">
         <v>-18</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>5.53000020980835</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="I90" t="n">
-        <v>3.616636390813651</v>
+        <v>3.66300363741163</v>
       </c>
       <c r="J90" t="n">
         <v>-18</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>24.71999931335449</v>
+        <v>24.63999938964844</v>
       </c>
       <c r="I91" t="n">
-        <v>4.045307555731887</v>
+        <v>4.058441658972249</v>
       </c>
       <c r="J91" t="n">
         <v>-18</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>4.860000133514404</v>
+        <v>4.760000228881836</v>
       </c>
       <c r="I92" t="n">
-        <v>4.423868191224254</v>
+        <v>4.516806505501057</v>
       </c>
       <c r="J92" t="n">
         <v>-18</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>23.44000053405762</v>
+        <v>23.54999923706055</v>
       </c>
       <c r="I93" t="n">
-        <v>1.151877106861402</v>
+        <v>1.146496852429201</v>
       </c>
       <c r="J93" t="n">
         <v>-18</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>9.960000038146973</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="I94" t="n">
-        <v>2.008032120823259</v>
+        <v>1.98019794501133</v>
       </c>
       <c r="J94" t="n">
         <v>-18</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>8.689999580383301</v>
+        <v>8.505000114440918</v>
       </c>
       <c r="I95" t="n">
-        <v>2.761795300218116</v>
+        <v>2.821869450565864</v>
       </c>
       <c r="J95" t="n">
         <v>-18</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>21.20000076293945</v>
+        <v>20.94000053405762</v>
       </c>
       <c r="I96" t="n">
-        <v>3.726414960234482</v>
+        <v>3.772683762424522</v>
       </c>
       <c r="J96" t="n">
         <v>-18</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5.28000020980835</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="I97" t="n">
-        <v>1.761363566373337</v>
+        <v>1.722222191806684</v>
       </c>
       <c r="J97" t="n">
         <v>-18</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>35.02000045776367</v>
+        <v>34.34000015258789</v>
       </c>
       <c r="I99" t="n">
-        <v>0.999428884708674</v>
+        <v>1.019219564486879</v>
       </c>
       <c r="J99" t="n">
         <v>-18</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>6.815000057220459</v>
+        <v>6.71999979019165</v>
       </c>
       <c r="I100" t="n">
-        <v>8.133528911899596</v>
+        <v>8.248512162292668</v>
       </c>
       <c r="J100" t="n">
         <v>-18</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>2.279999971389771</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="I101" t="n">
-        <v>2.631578980390385</v>
+        <v>2.690582936628342</v>
       </c>
       <c r="J101" t="n">
         <v>-18</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>13.14999961853027</v>
+        <v>13.35000038146973</v>
       </c>
       <c r="I102" t="n">
-        <v>1.52091259164883</v>
+        <v>1.498127298015715</v>
       </c>
       <c r="J102" t="n">
         <v>-18</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>7.199999809265137</v>
+        <v>7.170000076293945</v>
       </c>
       <c r="I103" t="n">
-        <v>1.430555593452337</v>
+        <v>1.436541128368286</v>
       </c>
       <c r="J103" t="n">
         <v>-18</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>5.705999851226807</v>
+        <v>5.672999858856201</v>
       </c>
       <c r="I104" t="n">
-        <v>3.329828337782895</v>
+        <v>3.349198038554298</v>
       </c>
       <c r="J104" t="n">
         <v>-18</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>10.27000045776367</v>
+        <v>10.34000015258789</v>
       </c>
       <c r="I105" t="n">
-        <v>4.206426297414883</v>
+        <v>4.177949648210394</v>
       </c>
       <c r="J105" t="n">
         <v>-18</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>26.13999938964844</v>
+        <v>25.95999908447266</v>
       </c>
       <c r="I106" t="n">
-        <v>1.683244109692834</v>
+        <v>1.694915314011607</v>
       </c>
       <c r="J106" t="n">
         <v>-18</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>6.96999979019165</v>
+        <v>6.960000038146973</v>
       </c>
       <c r="I108" t="n">
-        <v>6.74318528189047</v>
+        <v>6.752873526206654</v>
       </c>
       <c r="J108" t="n">
         <v>-18</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>54.63999938964844</v>
+        <v>54.18000030517578</v>
       </c>
       <c r="I109" t="n">
-        <v>2.562225504463</v>
+        <v>2.583979313610781</v>
       </c>
       <c r="J109" t="n">
         <v>-18</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>3.41100001335144</v>
+        <v>3.365000009536743</v>
       </c>
       <c r="I110" t="n">
-        <v>8.795074723709494</v>
+        <v>8.915304580973856</v>
       </c>
       <c r="J110" t="n">
         <v>-18</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>15.35000038146973</v>
+        <v>15.80000019073486</v>
       </c>
       <c r="I111" t="n">
-        <v>0.7817589382268816</v>
+        <v>0.7594936617175999</v>
       </c>
       <c r="J111" t="n">
         <v>-18</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>3.430000066757202</v>
+        <v>3.400000095367432</v>
       </c>
       <c r="I112" t="n">
-        <v>4.95626812511178</v>
+        <v>4.999999859753782</v>
       </c>
       <c r="J112" t="n">
         <v>-18</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>22.60000038146973</v>
+        <v>22.14999961853027</v>
       </c>
       <c r="I113" t="n">
-        <v>3.097345080462682</v>
+        <v>3.160270934787706</v>
       </c>
       <c r="J113" t="n">
         <v>-18</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>2.559999942779541</v>
+        <v>2.579999923706055</v>
       </c>
       <c r="I114" t="n">
-        <v>1.367187530559023</v>
+        <v>1.356589187402923</v>
       </c>
       <c r="J114" t="n">
         <v>-18</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>5.579999923706055</v>
+        <v>5.550000190734863</v>
       </c>
       <c r="I115" t="n">
-        <v>5.913978575484007</v>
+        <v>5.945945741603757</v>
       </c>
       <c r="J115" t="n">
         <v>-18</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0.8949999809265137</v>
+        <v>0.8840000033378601</v>
       </c>
       <c r="I116" t="n">
-        <v>7.821229216958782</v>
+        <v>7.918552006299754</v>
       </c>
       <c r="J116" t="n">
         <v>-18</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>50.90000152587891</v>
+        <v>50.70000076293945</v>
       </c>
       <c r="I117" t="n">
-        <v>1.394891903174143</v>
+        <v>1.400394456244257</v>
       </c>
       <c r="J117" t="n">
         <v>-18</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>107</v>
+        <v>104.5999984741211</v>
       </c>
       <c r="I118" t="n">
-        <v>1.261682242990654</v>
+        <v>1.290630993970809</v>
       </c>
       <c r="J118" t="n">
         <v>-18</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>7.579999923706055</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="I119" t="n">
-        <v>1.055408981599118</v>
+        <v>1.095890382325411</v>
       </c>
       <c r="J119" t="n">
         <v>-18</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>4.527999877929688</v>
+        <v>4.403999805450439</v>
       </c>
       <c r="I121" t="n">
-        <v>3.754417062346039</v>
+        <v>3.860127327653514</v>
       </c>
       <c r="J121" t="n">
         <v>-18</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>58.5</v>
+        <v>59</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.7627118644067797</v>
       </c>
       <c r="J123" t="n">
         <v>-18</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>5.78000020980835</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6920414973709197</v>
+        <v>0.6896551497342619</v>
       </c>
       <c r="J124" t="n">
         <v>-18</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>38.91999816894531</v>
+        <v>37.77999877929688</v>
       </c>
       <c r="I125" t="n">
-        <v>2.697841853543062</v>
+        <v>2.779248369312789</v>
       </c>
       <c r="J125" t="n">
         <v>-18</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>17.73999977111816</v>
+        <v>17.29000091552734</v>
       </c>
       <c r="I127" t="n">
-        <v>2.142051887839728</v>
+        <v>2.197802081425801</v>
       </c>
       <c r="J127" t="n">
         <v>-18</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>27.65999984741211</v>
+        <v>27.10000038146973</v>
       </c>
       <c r="I128" t="n">
-        <v>2.169197408929619</v>
+        <v>2.214022109056</v>
       </c>
       <c r="J128" t="n">
         <v>-18</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>37.70000076293945</v>
+        <v>36.45000076293945</v>
       </c>
       <c r="I129" t="n">
-        <v>0.9283819440769439</v>
+        <v>0.9602194586395252</v>
       </c>
       <c r="J129" t="n">
         <v>-18</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>2.890000104904175</v>
+        <v>2.849999904632568</v>
       </c>
       <c r="I131" t="n">
-        <v>0.3460207486854598</v>
+        <v>0.3508772047235992</v>
       </c>
       <c r="J131" t="n">
         <v>-18</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>20.90999984741211</v>
+        <v>20.8700008392334</v>
       </c>
       <c r="I132" t="n">
-        <v>5.35628889609301</v>
+        <v>5.366554647638146</v>
       </c>
       <c r="J132" t="n">
         <v>-18</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>1.429999947547913</v>
+        <v>1.440000057220459</v>
       </c>
       <c r="I133" t="n">
-        <v>6.99300724950897</v>
+        <v>6.944444168497026</v>
       </c>
       <c r="J133" t="n">
         <v>-18</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>9.460000038146973</v>
+        <v>9.340000152587891</v>
       </c>
       <c r="I134" t="n">
-        <v>2.748414365238511</v>
+        <v>2.783725864586418</v>
       </c>
       <c r="J134" t="n">
         <v>-18</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>2.223999977111816</v>
+        <v>2.186000108718872</v>
       </c>
       <c r="I135" t="n">
-        <v>4.150179898826474</v>
+        <v>4.222323669237755</v>
       </c>
       <c r="J135" t="n">
         <v>-18</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>9.100000381469727</v>
+        <v>9.119999885559082</v>
       </c>
       <c r="I136" t="n">
-        <v>3.846153684924045</v>
+        <v>3.837719346402645</v>
       </c>
       <c r="J136" t="n">
         <v>-25</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>6.550000190734863</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="I137" t="n">
-        <v>1.465648812282393</v>
+        <v>1.548387144408292</v>
       </c>
       <c r="J137" t="n">
         <v>-25</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>6.300000190734863</v>
+        <v>6.150000095367432</v>
       </c>
       <c r="I138" t="n">
-        <v>4.761904617736313</v>
+        <v>4.878048704844394</v>
       </c>
       <c r="J138" t="n">
         <v>-25</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>18.71999931335449</v>
+        <v>18.63999938964844</v>
       </c>
       <c r="I141" t="n">
-        <v>2.670940268909676</v>
+        <v>2.682403521309506</v>
       </c>
       <c r="J141" t="n">
         <v>-25</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>15.39999961853027</v>
+        <v>15.11999988555908</v>
       </c>
       <c r="I143" t="n">
-        <v>3.246753327177799</v>
+        <v>3.306878331907552</v>
       </c>
       <c r="J143" t="n">
         <v>-25</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>3.660000085830688</v>
+        <v>3.680000066757202</v>
       </c>
       <c r="I144" t="n">
-        <v>2.73224037308468</v>
+        <v>2.71739125505287</v>
       </c>
       <c r="J144" t="n">
         <v>-25</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>3.180000066757202</v>
+        <v>3.160000085830688</v>
       </c>
       <c r="I145" t="n">
-        <v>3.459119424238636</v>
+        <v>3.481012563677942</v>
       </c>
       <c r="J145" t="n">
         <v>-25</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>4.909999847412109</v>
+        <v>4.949999809265137</v>
       </c>
       <c r="I147" t="n">
-        <v>1.934826944038933</v>
+        <v>1.919191993142792</v>
       </c>
       <c r="J147" t="n">
         <v>-25</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>1.350000023841858</v>
+        <v>1.330000042915344</v>
       </c>
       <c r="I148" t="n">
-        <v>2.222222182976366</v>
+        <v>2.255639024961259</v>
       </c>
       <c r="J148" t="n">
         <v>-25</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>8.449999809265137</v>
+        <v>8.149999618530273</v>
       </c>
       <c r="I149" t="n">
-        <v>1.065088781437818</v>
+        <v>1.104294530215329</v>
       </c>
       <c r="J149" t="n">
         <v>-25</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>7.090000152587891</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="I151" t="n">
-        <v>3.102961851414047</v>
+        <v>3.129445141310993</v>
       </c>
       <c r="J151" t="n">
         <v>-25</v>
